--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-op-planung.xlsx
+++ b/ci-build/StructureDefinition-senologie-op-planung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Operationsplanung</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1898,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AQ57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.09765625" customWidth="true" bestFit="true"/>
@@ -1936,11 +1942,13 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="73.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="140.125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="57.34375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="38.4921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="73.23046875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="140.125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="57.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2067,6 +2075,12 @@
       <c r="AO1" t="s" s="1">
         <v>77</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2077,14 +2091,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2096,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2156,39 +2170,45 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AP2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2196,10 +2216,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2208,19 +2228,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2270,13 +2290,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2297,15 +2317,21 @@
         <v>20</v>
       </c>
       <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2313,10 +2339,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2325,16 +2351,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2385,19 +2411,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2412,15 +2438,21 @@
         <v>20</v>
       </c>
       <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2428,31 +2460,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2502,19 +2534,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2529,15 +2561,21 @@
         <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2545,10 +2583,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2560,16 +2598,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2595,13 +2633,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2619,19 +2657,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2646,26 +2684,32 @@
         <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2677,16 +2721,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2736,19 +2780,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2757,32 +2801,38 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AP7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2794,16 +2844,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2853,13 +2903,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2874,21 +2924,27 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2896,10 +2952,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2911,13 +2967,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2956,29 +3012,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2993,28 +3049,34 @@
         <v>20</v>
       </c>
       <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -3026,16 +3088,16 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3085,19 +3147,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3112,28 +3174,34 @@
         <v>20</v>
       </c>
       <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3145,16 +3213,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3204,19 +3272,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3231,28 +3299,34 @@
         <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3264,13 +3338,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3321,19 +3395,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3348,28 +3422,34 @@
         <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3381,13 +3461,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3438,19 +3518,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3465,28 +3545,34 @@
         <v>20</v>
       </c>
       <c r="AO13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3498,16 +3584,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3557,19 +3643,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -3584,28 +3670,34 @@
         <v>20</v>
       </c>
       <c r="AO14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3617,16 +3709,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3676,19 +3768,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3703,50 +3795,56 @@
         <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3795,19 +3893,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3816,21 +3914,27 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3838,10 +3942,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3850,19 +3954,19 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3912,25 +4016,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>190</v>
@@ -3940,14 +4044,20 @@
       </c>
       <c r="AO17" t="s" s="2">
         <v>192</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>194</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3955,10 +4065,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3967,19 +4077,19 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4029,42 +4139,48 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>200</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="AO18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4072,10 +4188,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4084,19 +4200,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4146,53 +4262,59 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AO19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4201,16 +4323,16 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4261,53 +4383,59 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4316,16 +4444,16 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4376,53 +4504,59 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AO21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4431,22 +4565,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4495,42 +4629,48 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4538,31 +4678,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4588,13 +4728,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4612,25 +4752,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>240</v>
@@ -4640,14 +4780,20 @@
       </c>
       <c r="AO23" t="s" s="2">
         <v>242</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4655,31 +4801,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4687,7 +4833,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>20</v>
@@ -4705,13 +4851,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4729,42 +4875,48 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4772,34 +4924,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4824,13 +4976,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4848,42 +5000,48 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4891,10 +5049,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4903,16 +5061,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4920,7 +5078,7 @@
         <v>20</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>20</v>
@@ -4941,13 +5099,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4965,25 +5123,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>272</v>
@@ -4992,15 +5150,21 @@
         <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5008,152 +5172,158 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5179,13 +5349,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5203,25 +5373,25 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>292</v>
@@ -5231,14 +5401,20 @@
       </c>
       <c r="AO28" t="s" s="2">
         <v>294</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5246,10 +5422,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5261,13 +5437,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5318,13 +5494,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5339,32 +5515,38 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5376,16 +5558,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5423,31 +5605,31 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5456,21 +5638,27 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5478,10 +5666,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5490,22 +5678,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5554,42 +5742,48 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5597,10 +5791,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5609,22 +5803,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5673,53 +5867,59 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5728,19 +5928,19 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5766,13 +5966,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5790,42 +5990,48 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>294</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>296</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5833,10 +6039,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5845,20 +6051,20 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5907,42 +6113,48 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5950,28 +6162,28 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6022,25 +6234,25 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>344</v>
@@ -6050,25 +6262,31 @@
       </c>
       <c r="AO35" t="s" s="2">
         <v>346</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>348</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6077,16 +6295,16 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6137,25 +6355,25 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>354</v>
@@ -6165,25 +6383,31 @@
       </c>
       <c r="AO36" t="s" s="2">
         <v>356</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>358</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6192,16 +6416,16 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6252,25 +6476,25 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>364</v>
@@ -6280,14 +6504,20 @@
       </c>
       <c r="AO37" t="s" s="2">
         <v>366</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>368</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6295,10 +6525,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6307,16 +6537,16 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6343,13 +6573,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6367,19 +6597,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6388,32 +6618,38 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>376</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6422,16 +6658,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6482,25 +6718,25 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>382</v>
@@ -6510,25 +6746,31 @@
       </c>
       <c r="AO39" t="s" s="2">
         <v>384</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>386</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6537,19 +6779,19 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6599,25 +6841,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>393</v>
@@ -6627,25 +6869,31 @@
       </c>
       <c r="AO40" t="s" s="2">
         <v>395</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>397</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6654,19 +6902,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6692,13 +6940,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6716,25 +6964,25 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>405</v>
@@ -6743,26 +6991,32 @@
         <v>406</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6771,19 +7025,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6833,42 +7087,48 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AO42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6876,10 +7136,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6888,16 +7148,16 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6924,13 +7184,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6948,19 +7208,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6969,21 +7229,27 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6991,10 +7257,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7003,16 +7269,16 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7063,19 +7329,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7084,21 +7350,27 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7106,10 +7378,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7118,19 +7390,19 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7156,13 +7428,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7180,25 +7452,25 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>434</v>
@@ -7207,15 +7479,21 @@
         <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7223,10 +7501,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7235,19 +7513,19 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7297,42 +7575,48 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>443</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7340,10 +7624,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7355,13 +7639,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7412,53 +7696,59 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>450</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>451</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7470,16 +7760,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7529,42 +7819,48 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>458</v>
+        <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>459</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
+        <v>460</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7572,10 +7868,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7584,19 +7880,19 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7646,53 +7942,59 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
+        <v>467</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7701,22 +8003,22 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7741,13 +8043,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7765,42 +8067,48 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AO50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>478</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7808,10 +8116,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7823,13 +8131,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7880,13 +8188,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7901,32 +8209,38 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7938,16 +8252,16 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7985,31 +8299,31 @@
         <v>20</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8018,21 +8332,27 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8040,34 +8360,34 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8116,42 +8436,48 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="AO53" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8159,10 +8485,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8171,22 +8497,22 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8235,42 +8561,48 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8278,10 +8610,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8293,16 +8625,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8352,42 +8684,48 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>487</v>
+        <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>491</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8395,10 +8733,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8407,16 +8745,16 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8467,42 +8805,48 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>493</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8510,10 +8854,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8525,16 +8869,16 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8584,38 +8928,44 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>499</v>
+        <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO57">
+  <autoFilter ref="A1:AQ57">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
